--- a/output/review/local-2026-03-21/methemoglobin_review.xlsx
+++ b/output/review/local-2026-03-21/methemoglobin_review.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="methemoglobin" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'methemoglobin'!$A$12:$K$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'methemoglobin'!$A$12:$L$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,20 +443,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:L30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="50" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="50" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -592,59 +593,65 @@
       <c r="I12" s="1" t="n"/>
       <c r="J12" s="1" t="n"/>
       <c r="K12" s="1" t="n"/>
+      <c r="L12" s="1" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>LOINC</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>SCTID</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>FSN</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>PT</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Complete aggregation</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Quantitative (all numeric)</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>Quantitative &amp; convertible</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>Qualitative (ordinal / nominal / presence)</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>Semi-quantitative (test strip)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>Panel / order code (no Property)</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>Use case</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>Reason</t>
         </is>
@@ -653,27 +660,27 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>2613-8</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>112391010000106</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Presence of methemoglobin in blood at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Methemoglobin [Presence] in Blood</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -681,14 +688,14 @@
           <t>·</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
@@ -696,12 +703,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>qualitative</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>Ordinal/Nominal scale → qualitative</t>
         </is>
@@ -710,27 +722,27 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>2619-5</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>225921010000105</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>Presence of methemoglobin in erythrocyte at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Methemoglobin [Presence] in Red Blood Cells</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -738,14 +750,14 @@
           <t>·</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
@@ -753,12 +765,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>qualitative</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>Ordinal/Nominal scale → qualitative</t>
         </is>
@@ -767,32 +784,32 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>4534-4</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>742371010000107</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Mass fraction of cyanmethemoglobin to hemoglobin.total in blood at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Cyanmethemoglobin/Hemoglobin.total in Blood</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
@@ -810,12 +827,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -824,32 +846,32 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>2615-3</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>517551010000102</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>Mass fraction of methemoglobin to hemoglobin.total in arterial blood at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Methemoglobin/Hemoglobin.total in Arterial blood</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
@@ -867,12 +889,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -881,32 +908,32 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>72361-9</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>608471010000103</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>Mass fraction of methemoglobin to hemoglobin.total in arterial cord blood at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Methemoglobin/Hemoglobin.total in Arterial cord blood</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
@@ -924,12 +951,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -938,32 +970,32 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>97554-0</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>624201010000105</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>Mass fraction of methemoglobin to hemoglobin.total in BldCV at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Methemoglobin/Hemoglobin.total in Central venous blood</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
@@ -981,12 +1013,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -995,32 +1032,32 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>2614-6</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>517541010000104</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Mass fraction of methemoglobin to hemoglobin.total in blood at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Methemoglobin/Hemoglobin.total in Blood</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
@@ -1038,12 +1075,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -1052,32 +1094,32 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>2616-1</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>517561010000100</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>Mass fraction of methemoglobin to hemoglobin.total in capillary blood at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Methemoglobin/Hemoglobin.total in Capillary blood</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
@@ -1095,12 +1137,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -1109,32 +1156,32 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>55942-7</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>594651010000108</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>Mass fraction of methemoglobin to hemoglobin.total in cord blood at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Methemoglobin/Hemoglobin.total in Cord blood</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
@@ -1152,12 +1199,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -1166,32 +1218,32 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>2618-7</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>517581010000108</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>Mass fraction of methemoglobin to hemoglobin.total in erythrocyte at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Methemoglobin/Hemoglobin.total in Red Blood Cells</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
@@ -1209,12 +1261,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -1223,32 +1280,32 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>41607-3</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>539721010000102</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>Mass fraction of methemoglobin to hemoglobin.total in mixed venous blood at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Methemoglobin/Hemoglobin.total in Mixed venous blood</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
@@ -1266,12 +1323,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -1280,32 +1342,32 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>2617-9</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>517571010000105</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>Mass fraction of methemoglobin to hemoglobin.total in venous blood at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Methemoglobin/Hemoglobin.total in Venous blood</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
@@ -1323,12 +1385,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -1337,32 +1404,32 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>72360-1</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>608461010000108</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>Mass fraction of methemoglobin to hemoglobin.total in venous cord blood at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Methemoglobin/Hemoglobin.total in Venous cord blood</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
@@ -1380,12 +1447,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale</t>
         </is>
@@ -1394,32 +1466,32 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>109592-6</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>719541010000106</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>Measurement of methemoglobin in blood (observable entity)</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Methemoglobin [Measurement] in Blood</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
@@ -1437,12 +1509,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr">
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>quantitative</t>
         </is>
       </c>
-      <c r="K27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>Measurement property, no scale asserted (generic)</t>
         </is>
@@ -1451,24 +1528,24 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>15082-1</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>41771010000104</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>Mass concentration of methemoglobin in blood at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Methemoglobin [Mass/volume] in Blood</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1479,9 +1556,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G28" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
@@ -1494,12 +1571,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -1508,24 +1590,24 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>56040-9</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>184071010000100</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>Substance concentration of methemoglobin in blood at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Methemoglobin [Moles/volume] in Blood</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1536,9 +1618,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G29" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
@@ -1551,12 +1633,17 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
@@ -1565,24 +1652,24 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>72262-9</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>215401010000104</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>Substance concentration of methemoglobin in cerebrospinal fluid at point in time (observable entity)</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Methemoglobin [Moles/volume] in Cerebral spinal fluid</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1593,9 +1680,9 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="G30" s="4" t="inlineStr">
-        <is>
-          <t>·</t>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
@@ -1608,19 +1695,24 @@
           <t>·</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>quantitative_convertible</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>Quantitative scale + concentration property</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A12:K30"/>
+  <autoFilter ref="A12:L30"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>